--- a/data/Jabal Omar Hyatt Regency.xlsx
+++ b/data/Jabal Omar Hyatt Regency.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGR-TANTAWY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A396A8-C1AD-496D-8CE2-D3C8F8CC7513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF46A74B-D464-45D8-AAB9-D9CD7BE00B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="26" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1200,12 +1200,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1255,6 +1249,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1630,7 +1630,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -1728,7 +1728,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45108</v>
       </c>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -2275,7 +2275,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="13">
         <v>45108</v>
       </c>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -2900,7 +2900,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="13">
         <v>45108</v>
       </c>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -3419,7 +3419,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="17">
         <v>45108</v>
       </c>
@@ -3879,7 +3879,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="53">
@@ -4004,7 +4004,7 @@
       </c>
     </row>
     <row r="2" spans="1:31" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45597</v>
       </c>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="12" spans="1:31" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:31" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -4536,7 +4536,7 @@
       </c>
     </row>
     <row r="14" spans="1:31" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45597</v>
@@ -4992,22 +4992,22 @@
       <c r="N24" s="46"/>
       <c r="O24" s="23"/>
       <c r="P24" s="46"/>
-      <c r="Q24" s="110" t="s">
+      <c r="Q24" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
-      <c r="X24" s="111"/>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="111"/>
-      <c r="AA24" s="111"/>
-      <c r="AB24" s="111"/>
-      <c r="AC24" s="111"/>
-      <c r="AD24" s="111"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="128"/>
+      <c r="T24" s="128"/>
+      <c r="U24" s="128"/>
+      <c r="V24" s="128"/>
+      <c r="W24" s="128"/>
+      <c r="X24" s="128"/>
+      <c r="Y24" s="128"/>
+      <c r="Z24" s="128"/>
+      <c r="AA24" s="128"/>
+      <c r="AB24" s="128"/>
+      <c r="AC24" s="128"/>
+      <c r="AD24" s="128"/>
       <c r="AE24" s="129"/>
     </row>
     <row r="25" spans="1:33" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="27" spans="1:33" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -5205,7 +5205,7 @@
       </c>
     </row>
     <row r="29" spans="1:33" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45597</v>
@@ -5543,38 +5543,38 @@
       <c r="A36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="123" t="s">
+      <c r="B36" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="124"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
-      <c r="K36" s="124"/>
-      <c r="L36" s="124"/>
-      <c r="M36" s="124"/>
-      <c r="N36" s="124"/>
-      <c r="O36" s="124"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="124"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="124"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="124"/>
-      <c r="AB36" s="124"/>
-      <c r="AC36" s="124"/>
-      <c r="AD36" s="124"/>
-      <c r="AE36" s="124"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="122"/>
+      <c r="I36" s="122"/>
+      <c r="J36" s="122"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="122"/>
+      <c r="M36" s="122"/>
+      <c r="N36" s="122"/>
+      <c r="O36" s="122"/>
+      <c r="P36" s="122"/>
+      <c r="Q36" s="122"/>
+      <c r="R36" s="122"/>
+      <c r="S36" s="122"/>
+      <c r="T36" s="122"/>
+      <c r="U36" s="122"/>
+      <c r="V36" s="122"/>
+      <c r="W36" s="122"/>
+      <c r="X36" s="122"/>
+      <c r="Y36" s="122"/>
+      <c r="Z36" s="122"/>
+      <c r="AA36" s="122"/>
+      <c r="AB36" s="122"/>
+      <c r="AC36" s="122"/>
+      <c r="AD36" s="122"/>
+      <c r="AE36" s="122"/>
     </row>
     <row r="37" spans="1:31" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -5646,7 +5646,7 @@
     </row>
     <row r="39" spans="1:31" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:31" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -5771,7 +5771,7 @@
       </c>
     </row>
     <row r="41" spans="1:31" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45597</v>
@@ -6107,38 +6107,38 @@
       <c r="A48" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="123" t="s">
+      <c r="B48" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="124"/>
-      <c r="K48" s="124"/>
-      <c r="L48" s="124"/>
-      <c r="M48" s="124"/>
-      <c r="N48" s="124"/>
-      <c r="O48" s="124"/>
-      <c r="P48" s="124"/>
-      <c r="Q48" s="124"/>
-      <c r="R48" s="124"/>
-      <c r="S48" s="124"/>
-      <c r="T48" s="124"/>
-      <c r="U48" s="124"/>
-      <c r="V48" s="124"/>
-      <c r="W48" s="124"/>
-      <c r="X48" s="124"/>
-      <c r="Y48" s="124"/>
-      <c r="Z48" s="124"/>
-      <c r="AA48" s="124"/>
-      <c r="AB48" s="124"/>
-      <c r="AC48" s="124"/>
-      <c r="AD48" s="124"/>
-      <c r="AE48" s="124"/>
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="122"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="122"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="122"/>
+      <c r="S48" s="122"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="122"/>
+      <c r="V48" s="122"/>
+      <c r="W48" s="122"/>
+      <c r="X48" s="122"/>
+      <c r="Y48" s="122"/>
+      <c r="Z48" s="122"/>
+      <c r="AA48" s="122"/>
+      <c r="AB48" s="122"/>
+      <c r="AC48" s="122"/>
+      <c r="AD48" s="122"/>
+      <c r="AE48" s="122"/>
     </row>
     <row r="49" spans="1:31" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -6255,7 +6255,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="53">
@@ -6384,7 +6384,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45627</v>
       </c>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -6934,7 +6934,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45627</v>
@@ -7388,39 +7388,39 @@
       <c r="A24" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="124"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="124"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="124"/>
-      <c r="Q24" s="124"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
-      <c r="T24" s="124"/>
-      <c r="U24" s="124"/>
-      <c r="V24" s="124"/>
-      <c r="W24" s="124"/>
-      <c r="X24" s="124"/>
-      <c r="Y24" s="124"/>
-      <c r="Z24" s="124"/>
-      <c r="AA24" s="124"/>
-      <c r="AB24" s="124"/>
-      <c r="AC24" s="124"/>
-      <c r="AD24" s="124"/>
-      <c r="AE24" s="124"/>
-      <c r="AF24" s="125"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="122"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="122"/>
+      <c r="P24" s="122"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="122"/>
+      <c r="S24" s="122"/>
+      <c r="T24" s="122"/>
+      <c r="U24" s="122"/>
+      <c r="V24" s="122"/>
+      <c r="W24" s="122"/>
+      <c r="X24" s="122"/>
+      <c r="Y24" s="122"/>
+      <c r="Z24" s="122"/>
+      <c r="AA24" s="122"/>
+      <c r="AB24" s="122"/>
+      <c r="AC24" s="122"/>
+      <c r="AD24" s="122"/>
+      <c r="AE24" s="122"/>
+      <c r="AF24" s="123"/>
     </row>
     <row r="25" spans="1:34" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
@@ -7496,7 +7496,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -7625,7 +7625,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45627</v>
@@ -7973,39 +7973,39 @@
       <c r="A36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="123" t="s">
+      <c r="B36" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="124"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
-      <c r="K36" s="124"/>
-      <c r="L36" s="124"/>
-      <c r="M36" s="124"/>
-      <c r="N36" s="124"/>
-      <c r="O36" s="124"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="124"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="124"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="124"/>
-      <c r="AB36" s="124"/>
-      <c r="AC36" s="124"/>
-      <c r="AD36" s="124"/>
-      <c r="AE36" s="124"/>
-      <c r="AF36" s="125"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="122"/>
+      <c r="I36" s="122"/>
+      <c r="J36" s="122"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="122"/>
+      <c r="M36" s="122"/>
+      <c r="N36" s="122"/>
+      <c r="O36" s="122"/>
+      <c r="P36" s="122"/>
+      <c r="Q36" s="122"/>
+      <c r="R36" s="122"/>
+      <c r="S36" s="122"/>
+      <c r="T36" s="122"/>
+      <c r="U36" s="122"/>
+      <c r="V36" s="122"/>
+      <c r="W36" s="122"/>
+      <c r="X36" s="122"/>
+      <c r="Y36" s="122"/>
+      <c r="Z36" s="122"/>
+      <c r="AA36" s="122"/>
+      <c r="AB36" s="122"/>
+      <c r="AC36" s="122"/>
+      <c r="AD36" s="122"/>
+      <c r="AE36" s="122"/>
+      <c r="AF36" s="123"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -8079,7 +8079,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -8208,7 +8208,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45627</v>
@@ -8554,39 +8554,39 @@
       <c r="A48" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="123" t="s">
+      <c r="B48" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="124"/>
-      <c r="K48" s="124"/>
-      <c r="L48" s="124"/>
-      <c r="M48" s="124"/>
-      <c r="N48" s="124"/>
-      <c r="O48" s="124"/>
-      <c r="P48" s="124"/>
-      <c r="Q48" s="124"/>
-      <c r="R48" s="124"/>
-      <c r="S48" s="124"/>
-      <c r="T48" s="124"/>
-      <c r="U48" s="124"/>
-      <c r="V48" s="124"/>
-      <c r="W48" s="124"/>
-      <c r="X48" s="124"/>
-      <c r="Y48" s="124"/>
-      <c r="Z48" s="124"/>
-      <c r="AA48" s="124"/>
-      <c r="AB48" s="124"/>
-      <c r="AC48" s="124"/>
-      <c r="AD48" s="124"/>
-      <c r="AE48" s="124"/>
-      <c r="AF48" s="125"/>
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="122"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="122"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="122"/>
+      <c r="S48" s="122"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="122"/>
+      <c r="V48" s="122"/>
+      <c r="W48" s="122"/>
+      <c r="X48" s="122"/>
+      <c r="Y48" s="122"/>
+      <c r="Z48" s="122"/>
+      <c r="AA48" s="122"/>
+      <c r="AB48" s="122"/>
+      <c r="AC48" s="122"/>
+      <c r="AD48" s="122"/>
+      <c r="AE48" s="122"/>
+      <c r="AF48" s="123"/>
     </row>
     <row r="49" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -8705,7 +8705,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="53">
@@ -8834,7 +8834,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45658</v>
       </c>
@@ -9253,7 +9253,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -9382,7 +9382,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45658</v>
@@ -9836,39 +9836,39 @@
       <c r="A24" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="124"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="124"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="124"/>
-      <c r="Q24" s="124"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
-      <c r="T24" s="124"/>
-      <c r="U24" s="124"/>
-      <c r="V24" s="124"/>
-      <c r="W24" s="124"/>
-      <c r="X24" s="124"/>
-      <c r="Y24" s="124"/>
-      <c r="Z24" s="124"/>
-      <c r="AA24" s="124"/>
-      <c r="AB24" s="124"/>
-      <c r="AC24" s="124"/>
-      <c r="AD24" s="124"/>
-      <c r="AE24" s="124"/>
-      <c r="AF24" s="125"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="122"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="122"/>
+      <c r="P24" s="122"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="122"/>
+      <c r="S24" s="122"/>
+      <c r="T24" s="122"/>
+      <c r="U24" s="122"/>
+      <c r="V24" s="122"/>
+      <c r="W24" s="122"/>
+      <c r="X24" s="122"/>
+      <c r="Y24" s="122"/>
+      <c r="Z24" s="122"/>
+      <c r="AA24" s="122"/>
+      <c r="AB24" s="122"/>
+      <c r="AC24" s="122"/>
+      <c r="AD24" s="122"/>
+      <c r="AE24" s="122"/>
+      <c r="AF24" s="123"/>
     </row>
     <row r="25" spans="1:34" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
@@ -9944,7 +9944,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -10073,7 +10073,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45658</v>
@@ -10421,39 +10421,39 @@
       <c r="A36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="123" t="s">
+      <c r="B36" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="124"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
-      <c r="K36" s="124"/>
-      <c r="L36" s="124"/>
-      <c r="M36" s="124"/>
-      <c r="N36" s="124"/>
-      <c r="O36" s="124"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="124"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="124"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="124"/>
-      <c r="AB36" s="124"/>
-      <c r="AC36" s="124"/>
-      <c r="AD36" s="124"/>
-      <c r="AE36" s="124"/>
-      <c r="AF36" s="125"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="122"/>
+      <c r="I36" s="122"/>
+      <c r="J36" s="122"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="122"/>
+      <c r="M36" s="122"/>
+      <c r="N36" s="122"/>
+      <c r="O36" s="122"/>
+      <c r="P36" s="122"/>
+      <c r="Q36" s="122"/>
+      <c r="R36" s="122"/>
+      <c r="S36" s="122"/>
+      <c r="T36" s="122"/>
+      <c r="U36" s="122"/>
+      <c r="V36" s="122"/>
+      <c r="W36" s="122"/>
+      <c r="X36" s="122"/>
+      <c r="Y36" s="122"/>
+      <c r="Z36" s="122"/>
+      <c r="AA36" s="122"/>
+      <c r="AB36" s="122"/>
+      <c r="AC36" s="122"/>
+      <c r="AD36" s="122"/>
+      <c r="AE36" s="122"/>
+      <c r="AF36" s="123"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -10527,7 +10527,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -10656,7 +10656,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45658</v>
@@ -11002,39 +11002,39 @@
       <c r="A48" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="123" t="s">
+      <c r="B48" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="124"/>
-      <c r="K48" s="124"/>
-      <c r="L48" s="124"/>
-      <c r="M48" s="124"/>
-      <c r="N48" s="124"/>
-      <c r="O48" s="124"/>
-      <c r="P48" s="124"/>
-      <c r="Q48" s="124"/>
-      <c r="R48" s="124"/>
-      <c r="S48" s="124"/>
-      <c r="T48" s="124"/>
-      <c r="U48" s="124"/>
-      <c r="V48" s="124"/>
-      <c r="W48" s="124"/>
-      <c r="X48" s="124"/>
-      <c r="Y48" s="124"/>
-      <c r="Z48" s="124"/>
-      <c r="AA48" s="124"/>
-      <c r="AB48" s="124"/>
-      <c r="AC48" s="124"/>
-      <c r="AD48" s="124"/>
-      <c r="AE48" s="124"/>
-      <c r="AF48" s="125"/>
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="122"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="122"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="122"/>
+      <c r="S48" s="122"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="122"/>
+      <c r="V48" s="122"/>
+      <c r="W48" s="122"/>
+      <c r="X48" s="122"/>
+      <c r="Y48" s="122"/>
+      <c r="Z48" s="122"/>
+      <c r="AA48" s="122"/>
+      <c r="AB48" s="122"/>
+      <c r="AC48" s="122"/>
+      <c r="AD48" s="122"/>
+      <c r="AE48" s="122"/>
+      <c r="AF48" s="123"/>
     </row>
     <row r="49" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -11152,7 +11152,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="53">
@@ -11269,7 +11269,7 @@
       </c>
     </row>
     <row r="2" spans="1:29" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45689</v>
       </c>
@@ -11654,7 +11654,7 @@
     </row>
     <row r="12" spans="1:29" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -11771,7 +11771,7 @@
       </c>
     </row>
     <row r="14" spans="1:29" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45689</v>
@@ -12186,36 +12186,36 @@
       <c r="A24" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="124"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="124"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="124"/>
-      <c r="Q24" s="124"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
-      <c r="T24" s="124"/>
-      <c r="U24" s="124"/>
-      <c r="V24" s="124"/>
-      <c r="W24" s="124"/>
-      <c r="X24" s="124"/>
-      <c r="Y24" s="124"/>
-      <c r="Z24" s="124"/>
-      <c r="AA24" s="124"/>
-      <c r="AB24" s="124"/>
-      <c r="AC24" s="124"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="122"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="122"/>
+      <c r="P24" s="122"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="122"/>
+      <c r="S24" s="122"/>
+      <c r="T24" s="122"/>
+      <c r="U24" s="122"/>
+      <c r="V24" s="122"/>
+      <c r="W24" s="122"/>
+      <c r="X24" s="122"/>
+      <c r="Y24" s="122"/>
+      <c r="Z24" s="122"/>
+      <c r="AA24" s="122"/>
+      <c r="AB24" s="122"/>
+      <c r="AC24" s="122"/>
     </row>
     <row r="25" spans="1:31" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
@@ -12285,7 +12285,7 @@
     </row>
     <row r="27" spans="1:31" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -12402,7 +12402,7 @@
       </c>
     </row>
     <row r="29" spans="1:31" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45689</v>
@@ -12720,36 +12720,36 @@
       <c r="A36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="123" t="s">
+      <c r="B36" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="124"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
-      <c r="K36" s="124"/>
-      <c r="L36" s="124"/>
-      <c r="M36" s="124"/>
-      <c r="N36" s="124"/>
-      <c r="O36" s="124"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="124"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="124"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="124"/>
-      <c r="AB36" s="124"/>
-      <c r="AC36" s="124"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="122"/>
+      <c r="I36" s="122"/>
+      <c r="J36" s="122"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="122"/>
+      <c r="M36" s="122"/>
+      <c r="N36" s="122"/>
+      <c r="O36" s="122"/>
+      <c r="P36" s="122"/>
+      <c r="Q36" s="122"/>
+      <c r="R36" s="122"/>
+      <c r="S36" s="122"/>
+      <c r="T36" s="122"/>
+      <c r="U36" s="122"/>
+      <c r="V36" s="122"/>
+      <c r="W36" s="122"/>
+      <c r="X36" s="122"/>
+      <c r="Y36" s="122"/>
+      <c r="Z36" s="122"/>
+      <c r="AA36" s="122"/>
+      <c r="AB36" s="122"/>
+      <c r="AC36" s="122"/>
     </row>
     <row r="37" spans="1:29" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -12817,7 +12817,7 @@
     </row>
     <row r="39" spans="1:29" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:29" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -12934,7 +12934,7 @@
       </c>
     </row>
     <row r="41" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45689</v>
@@ -13250,36 +13250,36 @@
       <c r="A48" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="123" t="s">
+      <c r="B48" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="124"/>
-      <c r="K48" s="124"/>
-      <c r="L48" s="124"/>
-      <c r="M48" s="124"/>
-      <c r="N48" s="124"/>
-      <c r="O48" s="124"/>
-      <c r="P48" s="124"/>
-      <c r="Q48" s="124"/>
-      <c r="R48" s="124"/>
-      <c r="S48" s="124"/>
-      <c r="T48" s="124"/>
-      <c r="U48" s="124"/>
-      <c r="V48" s="124"/>
-      <c r="W48" s="124"/>
-      <c r="X48" s="124"/>
-      <c r="Y48" s="124"/>
-      <c r="Z48" s="124"/>
-      <c r="AA48" s="124"/>
-      <c r="AB48" s="124"/>
-      <c r="AC48" s="124"/>
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="122"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="122"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="122"/>
+      <c r="S48" s="122"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="122"/>
+      <c r="V48" s="122"/>
+      <c r="W48" s="122"/>
+      <c r="X48" s="122"/>
+      <c r="Y48" s="122"/>
+      <c r="Z48" s="122"/>
+      <c r="AA48" s="122"/>
+      <c r="AB48" s="122"/>
+      <c r="AC48" s="122"/>
     </row>
     <row r="49" spans="1:29" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -13393,7 +13393,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="53">
@@ -13522,7 +13522,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45717</v>
       </c>
@@ -13941,7 +13941,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -14070,7 +14070,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45717</v>
@@ -14524,36 +14524,36 @@
       <c r="A24" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="124"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="124"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="124"/>
-      <c r="Q24" s="124"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
-      <c r="T24" s="124"/>
-      <c r="U24" s="124"/>
-      <c r="V24" s="124"/>
-      <c r="W24" s="124"/>
-      <c r="X24" s="124"/>
-      <c r="Y24" s="124"/>
-      <c r="Z24" s="124"/>
-      <c r="AA24" s="124"/>
-      <c r="AB24" s="124"/>
-      <c r="AC24" s="124"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="122"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="122"/>
+      <c r="P24" s="122"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="122"/>
+      <c r="S24" s="122"/>
+      <c r="T24" s="122"/>
+      <c r="U24" s="122"/>
+      <c r="V24" s="122"/>
+      <c r="W24" s="122"/>
+      <c r="X24" s="122"/>
+      <c r="Y24" s="122"/>
+      <c r="Z24" s="122"/>
+      <c r="AA24" s="122"/>
+      <c r="AB24" s="122"/>
+      <c r="AC24" s="122"/>
     </row>
     <row r="25" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
@@ -14624,7 +14624,7 @@
     </row>
     <row r="27" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -14753,7 +14753,7 @@
       </c>
     </row>
     <row r="29" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45717</v>
@@ -15099,36 +15099,36 @@
       <c r="A36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="123" t="s">
+      <c r="B36" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="124"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
-      <c r="K36" s="124"/>
-      <c r="L36" s="124"/>
-      <c r="M36" s="124"/>
-      <c r="N36" s="124"/>
-      <c r="O36" s="124"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="124"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="124"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="124"/>
-      <c r="AB36" s="124"/>
-      <c r="AC36" s="124"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="122"/>
+      <c r="I36" s="122"/>
+      <c r="J36" s="122"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="122"/>
+      <c r="M36" s="122"/>
+      <c r="N36" s="122"/>
+      <c r="O36" s="122"/>
+      <c r="P36" s="122"/>
+      <c r="Q36" s="122"/>
+      <c r="R36" s="122"/>
+      <c r="S36" s="122"/>
+      <c r="T36" s="122"/>
+      <c r="U36" s="122"/>
+      <c r="V36" s="122"/>
+      <c r="W36" s="122"/>
+      <c r="X36" s="122"/>
+      <c r="Y36" s="122"/>
+      <c r="Z36" s="122"/>
+      <c r="AA36" s="122"/>
+      <c r="AB36" s="122"/>
+      <c r="AC36" s="122"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -15199,7 +15199,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -15328,7 +15328,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45717</v>
@@ -15674,36 +15674,36 @@
       <c r="A48" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="123" t="s">
+      <c r="B48" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="124"/>
-      <c r="K48" s="124"/>
-      <c r="L48" s="124"/>
-      <c r="M48" s="124"/>
-      <c r="N48" s="124"/>
-      <c r="O48" s="124"/>
-      <c r="P48" s="124"/>
-      <c r="Q48" s="124"/>
-      <c r="R48" s="124"/>
-      <c r="S48" s="124"/>
-      <c r="T48" s="124"/>
-      <c r="U48" s="124"/>
-      <c r="V48" s="124"/>
-      <c r="W48" s="124"/>
-      <c r="X48" s="124"/>
-      <c r="Y48" s="124"/>
-      <c r="Z48" s="124"/>
-      <c r="AA48" s="124"/>
-      <c r="AB48" s="124"/>
-      <c r="AC48" s="124"/>
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="122"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="122"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="122"/>
+      <c r="S48" s="122"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="122"/>
+      <c r="V48" s="122"/>
+      <c r="W48" s="122"/>
+      <c r="X48" s="122"/>
+      <c r="Y48" s="122"/>
+      <c r="Z48" s="122"/>
+      <c r="AA48" s="122"/>
+      <c r="AB48" s="122"/>
+      <c r="AC48" s="122"/>
     </row>
     <row r="49" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -15820,7 +15820,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -15949,7 +15949,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45809</v>
       </c>
@@ -16401,7 +16401,7 @@
       <c r="AF12" s="75"/>
     </row>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -16530,7 +16530,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45809</v>
@@ -16984,36 +16984,36 @@
       <c r="A24" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="111"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
-      <c r="X24" s="111"/>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="111"/>
-      <c r="AA24" s="111"/>
-      <c r="AB24" s="111"/>
-      <c r="AC24" s="111"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="128"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="128"/>
+      <c r="T24" s="128"/>
+      <c r="U24" s="128"/>
+      <c r="V24" s="128"/>
+      <c r="W24" s="128"/>
+      <c r="X24" s="128"/>
+      <c r="Y24" s="128"/>
+      <c r="Z24" s="128"/>
+      <c r="AA24" s="128"/>
+      <c r="AB24" s="128"/>
+      <c r="AC24" s="128"/>
       <c r="AF24" s="80"/>
     </row>
     <row r="25" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -17093,7 +17093,7 @@
       <c r="AF27" s="75"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -17222,7 +17222,7 @@
       </c>
     </row>
     <row r="29" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45809</v>
@@ -17568,36 +17568,36 @@
       <c r="A36" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="110" t="s">
+      <c r="B36" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="111"/>
-      <c r="N36" s="111"/>
-      <c r="O36" s="111"/>
-      <c r="P36" s="111"/>
-      <c r="Q36" s="111"/>
-      <c r="R36" s="111"/>
-      <c r="S36" s="111"/>
-      <c r="T36" s="111"/>
-      <c r="U36" s="111"/>
-      <c r="V36" s="111"/>
-      <c r="W36" s="111"/>
-      <c r="X36" s="111"/>
-      <c r="Y36" s="111"/>
-      <c r="Z36" s="111"/>
-      <c r="AA36" s="111"/>
-      <c r="AB36" s="111"/>
-      <c r="AC36" s="111"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="128"/>
+      <c r="O36" s="128"/>
+      <c r="P36" s="128"/>
+      <c r="Q36" s="128"/>
+      <c r="R36" s="128"/>
+      <c r="S36" s="128"/>
+      <c r="T36" s="128"/>
+      <c r="U36" s="128"/>
+      <c r="V36" s="128"/>
+      <c r="W36" s="128"/>
+      <c r="X36" s="128"/>
+      <c r="Y36" s="128"/>
+      <c r="Z36" s="128"/>
+      <c r="AA36" s="128"/>
+      <c r="AB36" s="128"/>
+      <c r="AC36" s="128"/>
       <c r="AF36" s="80"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -17675,7 +17675,7 @@
       <c r="AF39" s="75"/>
     </row>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -17804,7 +17804,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45809</v>
@@ -18150,36 +18150,36 @@
       <c r="A48" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="110" t="s">
+      <c r="B48" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="111"/>
-      <c r="D48" s="111"/>
-      <c r="E48" s="111"/>
-      <c r="F48" s="111"/>
-      <c r="G48" s="111"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="111"/>
-      <c r="L48" s="111"/>
-      <c r="M48" s="111"/>
-      <c r="N48" s="111"/>
-      <c r="O48" s="111"/>
-      <c r="P48" s="111"/>
-      <c r="Q48" s="111"/>
-      <c r="R48" s="111"/>
-      <c r="S48" s="111"/>
-      <c r="T48" s="111"/>
-      <c r="U48" s="111"/>
-      <c r="V48" s="111"/>
-      <c r="W48" s="111"/>
-      <c r="X48" s="111"/>
-      <c r="Y48" s="111"/>
-      <c r="Z48" s="111"/>
-      <c r="AA48" s="111"/>
-      <c r="AB48" s="111"/>
-      <c r="AC48" s="111"/>
+      <c r="C48" s="128"/>
+      <c r="D48" s="128"/>
+      <c r="E48" s="128"/>
+      <c r="F48" s="128"/>
+      <c r="G48" s="128"/>
+      <c r="H48" s="128"/>
+      <c r="I48" s="128"/>
+      <c r="J48" s="128"/>
+      <c r="K48" s="128"/>
+      <c r="L48" s="128"/>
+      <c r="M48" s="128"/>
+      <c r="N48" s="128"/>
+      <c r="O48" s="128"/>
+      <c r="P48" s="128"/>
+      <c r="Q48" s="128"/>
+      <c r="R48" s="128"/>
+      <c r="S48" s="128"/>
+      <c r="T48" s="128"/>
+      <c r="U48" s="128"/>
+      <c r="V48" s="128"/>
+      <c r="W48" s="128"/>
+      <c r="X48" s="128"/>
+      <c r="Y48" s="128"/>
+      <c r="Z48" s="128"/>
+      <c r="AA48" s="128"/>
+      <c r="AB48" s="128"/>
+      <c r="AC48" s="128"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="80"/>
@@ -18302,7 +18302,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -18431,7 +18431,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45839</v>
       </c>
@@ -18883,7 +18883,7 @@
       <c r="AF12" s="75"/>
     </row>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -19012,7 +19012,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45839</v>
@@ -19466,36 +19466,36 @@
       <c r="A24" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="111"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
-      <c r="X24" s="111"/>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="111"/>
-      <c r="AA24" s="111"/>
-      <c r="AB24" s="111"/>
-      <c r="AC24" s="111"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="128"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="128"/>
+      <c r="T24" s="128"/>
+      <c r="U24" s="128"/>
+      <c r="V24" s="128"/>
+      <c r="W24" s="128"/>
+      <c r="X24" s="128"/>
+      <c r="Y24" s="128"/>
+      <c r="Z24" s="128"/>
+      <c r="AA24" s="128"/>
+      <c r="AB24" s="128"/>
+      <c r="AC24" s="128"/>
       <c r="AF24" s="80"/>
     </row>
     <row r="25" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -19575,7 +19575,7 @@
       <c r="AF27" s="75"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -19704,7 +19704,7 @@
       </c>
     </row>
     <row r="29" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45839</v>
@@ -20050,36 +20050,36 @@
       <c r="A36" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="110" t="s">
+      <c r="B36" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="111"/>
-      <c r="N36" s="111"/>
-      <c r="O36" s="111"/>
-      <c r="P36" s="111"/>
-      <c r="Q36" s="111"/>
-      <c r="R36" s="111"/>
-      <c r="S36" s="111"/>
-      <c r="T36" s="111"/>
-      <c r="U36" s="111"/>
-      <c r="V36" s="111"/>
-      <c r="W36" s="111"/>
-      <c r="X36" s="111"/>
-      <c r="Y36" s="111"/>
-      <c r="Z36" s="111"/>
-      <c r="AA36" s="111"/>
-      <c r="AB36" s="111"/>
-      <c r="AC36" s="111"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="128"/>
+      <c r="O36" s="128"/>
+      <c r="P36" s="128"/>
+      <c r="Q36" s="128"/>
+      <c r="R36" s="128"/>
+      <c r="S36" s="128"/>
+      <c r="T36" s="128"/>
+      <c r="U36" s="128"/>
+      <c r="V36" s="128"/>
+      <c r="W36" s="128"/>
+      <c r="X36" s="128"/>
+      <c r="Y36" s="128"/>
+      <c r="Z36" s="128"/>
+      <c r="AA36" s="128"/>
+      <c r="AB36" s="128"/>
+      <c r="AC36" s="128"/>
       <c r="AF36" s="80"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -20157,7 +20157,7 @@
       <c r="AF39" s="75"/>
     </row>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -20286,7 +20286,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45839</v>
@@ -20632,36 +20632,36 @@
       <c r="A48" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="110" t="s">
+      <c r="B48" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="111"/>
-      <c r="D48" s="111"/>
-      <c r="E48" s="111"/>
-      <c r="F48" s="111"/>
-      <c r="G48" s="111"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="111"/>
-      <c r="L48" s="111"/>
-      <c r="M48" s="111"/>
-      <c r="N48" s="111"/>
-      <c r="O48" s="111"/>
-      <c r="P48" s="111"/>
-      <c r="Q48" s="111"/>
-      <c r="R48" s="111"/>
-      <c r="S48" s="111"/>
-      <c r="T48" s="111"/>
-      <c r="U48" s="111"/>
-      <c r="V48" s="111"/>
-      <c r="W48" s="111"/>
-      <c r="X48" s="111"/>
-      <c r="Y48" s="111"/>
-      <c r="Z48" s="111"/>
-      <c r="AA48" s="111"/>
-      <c r="AB48" s="111"/>
-      <c r="AC48" s="111"/>
+      <c r="C48" s="128"/>
+      <c r="D48" s="128"/>
+      <c r="E48" s="128"/>
+      <c r="F48" s="128"/>
+      <c r="G48" s="128"/>
+      <c r="H48" s="128"/>
+      <c r="I48" s="128"/>
+      <c r="J48" s="128"/>
+      <c r="K48" s="128"/>
+      <c r="L48" s="128"/>
+      <c r="M48" s="128"/>
+      <c r="N48" s="128"/>
+      <c r="O48" s="128"/>
+      <c r="P48" s="128"/>
+      <c r="Q48" s="128"/>
+      <c r="R48" s="128"/>
+      <c r="S48" s="128"/>
+      <c r="T48" s="128"/>
+      <c r="U48" s="128"/>
+      <c r="V48" s="128"/>
+      <c r="W48" s="128"/>
+      <c r="X48" s="128"/>
+      <c r="Y48" s="128"/>
+      <c r="Z48" s="128"/>
+      <c r="AA48" s="128"/>
+      <c r="AB48" s="128"/>
+      <c r="AC48" s="128"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="80"/>
@@ -20784,7 +20784,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -20913,7 +20913,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45870</v>
       </c>
@@ -21365,7 +21365,7 @@
       <c r="AF12" s="75"/>
     </row>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -21494,7 +21494,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45870</v>
@@ -21948,36 +21948,36 @@
       <c r="A24" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="111"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
-      <c r="X24" s="111"/>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="111"/>
-      <c r="AA24" s="111"/>
-      <c r="AB24" s="111"/>
-      <c r="AC24" s="111"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="128"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="128"/>
+      <c r="T24" s="128"/>
+      <c r="U24" s="128"/>
+      <c r="V24" s="128"/>
+      <c r="W24" s="128"/>
+      <c r="X24" s="128"/>
+      <c r="Y24" s="128"/>
+      <c r="Z24" s="128"/>
+      <c r="AA24" s="128"/>
+      <c r="AB24" s="128"/>
+      <c r="AC24" s="128"/>
       <c r="AF24" s="80"/>
     </row>
     <row r="25" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -22055,7 +22055,7 @@
       <c r="AF27" s="75"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -22184,7 +22184,7 @@
       </c>
     </row>
     <row r="29" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45870</v>
@@ -22530,36 +22530,36 @@
       <c r="A36" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="110" t="s">
+      <c r="B36" s="127" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="111"/>
-      <c r="N36" s="111"/>
-      <c r="O36" s="111"/>
-      <c r="P36" s="111"/>
-      <c r="Q36" s="111"/>
-      <c r="R36" s="111"/>
-      <c r="S36" s="111"/>
-      <c r="T36" s="111"/>
-      <c r="U36" s="111"/>
-      <c r="V36" s="111"/>
-      <c r="W36" s="111"/>
-      <c r="X36" s="111"/>
-      <c r="Y36" s="111"/>
-      <c r="Z36" s="111"/>
-      <c r="AA36" s="111"/>
-      <c r="AB36" s="111"/>
-      <c r="AC36" s="111"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="128"/>
+      <c r="O36" s="128"/>
+      <c r="P36" s="128"/>
+      <c r="Q36" s="128"/>
+      <c r="R36" s="128"/>
+      <c r="S36" s="128"/>
+      <c r="T36" s="128"/>
+      <c r="U36" s="128"/>
+      <c r="V36" s="128"/>
+      <c r="W36" s="128"/>
+      <c r="X36" s="128"/>
+      <c r="Y36" s="128"/>
+      <c r="Z36" s="128"/>
+      <c r="AA36" s="128"/>
+      <c r="AB36" s="128"/>
+      <c r="AC36" s="128"/>
       <c r="AF36" s="80"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -22637,7 +22637,7 @@
       <c r="AF39" s="75"/>
     </row>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -22766,7 +22766,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45870</v>
@@ -23112,36 +23112,36 @@
       <c r="A48" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="110" t="s">
+      <c r="B48" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="111"/>
-      <c r="D48" s="111"/>
-      <c r="E48" s="111"/>
-      <c r="F48" s="111"/>
-      <c r="G48" s="111"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="111"/>
-      <c r="L48" s="111"/>
-      <c r="M48" s="111"/>
-      <c r="N48" s="111"/>
-      <c r="O48" s="111"/>
-      <c r="P48" s="111"/>
-      <c r="Q48" s="111"/>
-      <c r="R48" s="111"/>
-      <c r="S48" s="111"/>
-      <c r="T48" s="111"/>
-      <c r="U48" s="111"/>
-      <c r="V48" s="111"/>
-      <c r="W48" s="111"/>
-      <c r="X48" s="111"/>
-      <c r="Y48" s="111"/>
-      <c r="Z48" s="111"/>
-      <c r="AA48" s="111"/>
-      <c r="AB48" s="111"/>
-      <c r="AC48" s="111"/>
+      <c r="C48" s="128"/>
+      <c r="D48" s="128"/>
+      <c r="E48" s="128"/>
+      <c r="F48" s="128"/>
+      <c r="G48" s="128"/>
+      <c r="H48" s="128"/>
+      <c r="I48" s="128"/>
+      <c r="J48" s="128"/>
+      <c r="K48" s="128"/>
+      <c r="L48" s="128"/>
+      <c r="M48" s="128"/>
+      <c r="N48" s="128"/>
+      <c r="O48" s="128"/>
+      <c r="P48" s="128"/>
+      <c r="Q48" s="128"/>
+      <c r="R48" s="128"/>
+      <c r="S48" s="128"/>
+      <c r="T48" s="128"/>
+      <c r="U48" s="128"/>
+      <c r="V48" s="128"/>
+      <c r="W48" s="128"/>
+      <c r="X48" s="128"/>
+      <c r="Y48" s="128"/>
+      <c r="Z48" s="128"/>
+      <c r="AA48" s="128"/>
+      <c r="AB48" s="128"/>
+      <c r="AC48" s="128"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="80"/>
@@ -23264,7 +23264,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -23393,7 +23393,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45901</v>
       </c>
@@ -23845,7 +23845,7 @@
       <c r="AF12" s="75"/>
     </row>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -23974,7 +23974,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45901</v>
@@ -24427,36 +24427,36 @@
       <c r="A24" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="111"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
-      <c r="X24" s="111"/>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="111"/>
-      <c r="AA24" s="111"/>
-      <c r="AB24" s="111"/>
-      <c r="AC24" s="111"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="128"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="128"/>
+      <c r="T24" s="128"/>
+      <c r="U24" s="128"/>
+      <c r="V24" s="128"/>
+      <c r="W24" s="128"/>
+      <c r="X24" s="128"/>
+      <c r="Y24" s="128"/>
+      <c r="Z24" s="128"/>
+      <c r="AA24" s="128"/>
+      <c r="AB24" s="128"/>
+      <c r="AC24" s="128"/>
       <c r="AF24" s="80"/>
     </row>
     <row r="25" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -24536,7 +24536,7 @@
       <c r="AF27" s="75"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -24665,7 +24665,7 @@
       </c>
     </row>
     <row r="29" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45901</v>
@@ -25011,36 +25011,36 @@
       <c r="A36" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="110" t="s">
+      <c r="B36" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="111"/>
-      <c r="N36" s="111"/>
-      <c r="O36" s="111"/>
-      <c r="P36" s="111"/>
-      <c r="Q36" s="111"/>
-      <c r="R36" s="111"/>
-      <c r="S36" s="111"/>
-      <c r="T36" s="111"/>
-      <c r="U36" s="111"/>
-      <c r="V36" s="111"/>
-      <c r="W36" s="111"/>
-      <c r="X36" s="111"/>
-      <c r="Y36" s="111"/>
-      <c r="Z36" s="111"/>
-      <c r="AA36" s="111"/>
-      <c r="AB36" s="111"/>
-      <c r="AC36" s="111"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="128"/>
+      <c r="O36" s="128"/>
+      <c r="P36" s="128"/>
+      <c r="Q36" s="128"/>
+      <c r="R36" s="128"/>
+      <c r="S36" s="128"/>
+      <c r="T36" s="128"/>
+      <c r="U36" s="128"/>
+      <c r="V36" s="128"/>
+      <c r="W36" s="128"/>
+      <c r="X36" s="128"/>
+      <c r="Y36" s="128"/>
+      <c r="Z36" s="128"/>
+      <c r="AA36" s="128"/>
+      <c r="AB36" s="128"/>
+      <c r="AC36" s="128"/>
       <c r="AF36" s="80"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -25118,7 +25118,7 @@
       <c r="AF39" s="75"/>
     </row>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -25247,7 +25247,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45901</v>
@@ -25593,36 +25593,36 @@
       <c r="A48" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="110" t="s">
+      <c r="B48" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="111"/>
-      <c r="D48" s="111"/>
-      <c r="E48" s="111"/>
-      <c r="F48" s="111"/>
-      <c r="G48" s="111"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="111"/>
-      <c r="L48" s="111"/>
-      <c r="M48" s="111"/>
-      <c r="N48" s="111"/>
-      <c r="O48" s="111"/>
-      <c r="P48" s="111"/>
-      <c r="Q48" s="111"/>
-      <c r="R48" s="111"/>
-      <c r="S48" s="111"/>
-      <c r="T48" s="111"/>
-      <c r="U48" s="111"/>
-      <c r="V48" s="111"/>
-      <c r="W48" s="111"/>
-      <c r="X48" s="111"/>
-      <c r="Y48" s="111"/>
-      <c r="Z48" s="111"/>
-      <c r="AA48" s="111"/>
-      <c r="AB48" s="111"/>
-      <c r="AC48" s="111"/>
+      <c r="C48" s="128"/>
+      <c r="D48" s="128"/>
+      <c r="E48" s="128"/>
+      <c r="F48" s="128"/>
+      <c r="G48" s="128"/>
+      <c r="H48" s="128"/>
+      <c r="I48" s="128"/>
+      <c r="J48" s="128"/>
+      <c r="K48" s="128"/>
+      <c r="L48" s="128"/>
+      <c r="M48" s="128"/>
+      <c r="N48" s="128"/>
+      <c r="O48" s="128"/>
+      <c r="P48" s="128"/>
+      <c r="Q48" s="128"/>
+      <c r="R48" s="128"/>
+      <c r="S48" s="128"/>
+      <c r="T48" s="128"/>
+      <c r="U48" s="128"/>
+      <c r="V48" s="128"/>
+      <c r="W48" s="128"/>
+      <c r="X48" s="128"/>
+      <c r="Y48" s="128"/>
+      <c r="Z48" s="128"/>
+      <c r="AA48" s="128"/>
+      <c r="AB48" s="128"/>
+      <c r="AC48" s="128"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="80"/>
@@ -25746,7 +25746,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -25875,7 +25875,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45962</v>
       </c>
@@ -26327,7 +26327,7 @@
       <c r="AF12" s="75"/>
     </row>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -26456,7 +26456,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45962</v>
@@ -26983,7 +26983,7 @@
       <c r="AF26" s="75"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="55">
@@ -27112,7 +27112,7 @@
       </c>
     </row>
     <row r="28" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="117"/>
+      <c r="A28" s="115"/>
       <c r="B28" s="30">
         <f>B2</f>
         <v>45962</v>
@@ -27460,36 +27460,36 @@
       <c r="A35" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="111"/>
-      <c r="S35" s="111"/>
-      <c r="T35" s="111"/>
-      <c r="U35" s="111"/>
-      <c r="V35" s="111"/>
-      <c r="W35" s="111"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="111"/>
-      <c r="AA35" s="111"/>
-      <c r="AB35" s="111"/>
-      <c r="AC35" s="111"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="128"/>
+      <c r="S35" s="128"/>
+      <c r="T35" s="128"/>
+      <c r="U35" s="128"/>
+      <c r="V35" s="128"/>
+      <c r="W35" s="128"/>
+      <c r="X35" s="128"/>
+      <c r="Y35" s="128"/>
+      <c r="Z35" s="128"/>
+      <c r="AA35" s="128"/>
+      <c r="AB35" s="128"/>
+      <c r="AC35" s="128"/>
       <c r="AF35" s="80"/>
     </row>
     <row r="36" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -27567,7 +27567,7 @@
       <c r="AF38" s="75"/>
     </row>
     <row r="39" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="54">
@@ -27696,7 +27696,7 @@
       </c>
     </row>
     <row r="40" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="119"/>
+      <c r="A40" s="117"/>
       <c r="B40" s="30">
         <f>B2</f>
         <v>45962</v>
@@ -28042,36 +28042,36 @@
       <c r="A47" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="110" t="s">
+      <c r="B47" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
-      <c r="M47" s="111"/>
-      <c r="N47" s="111"/>
-      <c r="O47" s="111"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
-      <c r="R47" s="111"/>
-      <c r="S47" s="111"/>
-      <c r="T47" s="111"/>
-      <c r="U47" s="111"/>
-      <c r="V47" s="111"/>
-      <c r="W47" s="111"/>
-      <c r="X47" s="111"/>
-      <c r="Y47" s="111"/>
-      <c r="Z47" s="111"/>
-      <c r="AA47" s="111"/>
-      <c r="AB47" s="111"/>
-      <c r="AC47" s="111"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="128"/>
+      <c r="O47" s="128"/>
+      <c r="P47" s="128"/>
+      <c r="Q47" s="128"/>
+      <c r="R47" s="128"/>
+      <c r="S47" s="128"/>
+      <c r="T47" s="128"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="128"/>
+      <c r="W47" s="128"/>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="128"/>
+      <c r="Z47" s="128"/>
+      <c r="AA47" s="128"/>
+      <c r="AB47" s="128"/>
+      <c r="AC47" s="128"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="80"/>
@@ -28201,7 +28201,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -28299,7 +28299,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45139</v>
       </c>
@@ -28748,7 +28748,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -28846,7 +28846,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="13">
         <v>45139</v>
       </c>
@@ -29403,7 +29403,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -29501,7 +29501,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="13">
         <v>45139</v>
       </c>
@@ -29922,7 +29922,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -30020,7 +30020,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="17">
         <v>45139</v>
       </c>
@@ -30502,7 +30502,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -30631,7 +30631,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45992</v>
       </c>
@@ -31083,7 +31083,7 @@
       <c r="AF12" s="75"/>
     </row>
     <row r="13" spans="1:32" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -31212,7 +31212,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45992</v>
@@ -31739,7 +31739,7 @@
       <c r="AF26" s="75"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="55">
@@ -31868,7 +31868,7 @@
       </c>
     </row>
     <row r="28" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="117"/>
+      <c r="A28" s="115"/>
       <c r="B28" s="30">
         <f>B2</f>
         <v>45992</v>
@@ -32214,36 +32214,36 @@
       <c r="A35" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="111"/>
-      <c r="S35" s="111"/>
-      <c r="T35" s="111"/>
-      <c r="U35" s="111"/>
-      <c r="V35" s="111"/>
-      <c r="W35" s="111"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="111"/>
-      <c r="AA35" s="111"/>
-      <c r="AB35" s="111"/>
-      <c r="AC35" s="111"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="128"/>
+      <c r="S35" s="128"/>
+      <c r="T35" s="128"/>
+      <c r="U35" s="128"/>
+      <c r="V35" s="128"/>
+      <c r="W35" s="128"/>
+      <c r="X35" s="128"/>
+      <c r="Y35" s="128"/>
+      <c r="Z35" s="128"/>
+      <c r="AA35" s="128"/>
+      <c r="AB35" s="128"/>
+      <c r="AC35" s="128"/>
       <c r="AD35" s="23"/>
       <c r="AE35" s="108"/>
       <c r="AF35" s="35"/>
@@ -32323,7 +32323,7 @@
       <c r="AF38" s="75"/>
     </row>
     <row r="39" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="54">
@@ -32452,7 +32452,7 @@
       </c>
     </row>
     <row r="40" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="119"/>
+      <c r="A40" s="117"/>
       <c r="B40" s="30">
         <f>B2</f>
         <v>45992</v>
@@ -32798,36 +32798,36 @@
       <c r="A47" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="110" t="s">
+      <c r="B47" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
-      <c r="M47" s="111"/>
-      <c r="N47" s="111"/>
-      <c r="O47" s="111"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
-      <c r="R47" s="111"/>
-      <c r="S47" s="111"/>
-      <c r="T47" s="111"/>
-      <c r="U47" s="111"/>
-      <c r="V47" s="111"/>
-      <c r="W47" s="111"/>
-      <c r="X47" s="111"/>
-      <c r="Y47" s="111"/>
-      <c r="Z47" s="111"/>
-      <c r="AA47" s="111"/>
-      <c r="AB47" s="111"/>
-      <c r="AC47" s="111"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="128"/>
+      <c r="O47" s="128"/>
+      <c r="P47" s="128"/>
+      <c r="Q47" s="128"/>
+      <c r="R47" s="128"/>
+      <c r="S47" s="128"/>
+      <c r="T47" s="128"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="128"/>
+      <c r="W47" s="128"/>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="128"/>
+      <c r="Z47" s="128"/>
+      <c r="AA47" s="128"/>
+      <c r="AB47" s="128"/>
+      <c r="AC47" s="128"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="80"/>
@@ -32959,7 +32959,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -33088,7 +33088,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>46023</v>
       </c>
@@ -33540,7 +33540,7 @@
       <c r="AF12" s="75"/>
     </row>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -33669,7 +33669,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>46023</v>
@@ -34090,35 +34090,35 @@
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
-      <c r="E23" s="110" t="s">
+      <c r="E23" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="111"/>
-      <c r="N23" s="111"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="111"/>
-      <c r="S23" s="111"/>
-      <c r="T23" s="111"/>
-      <c r="U23" s="111"/>
-      <c r="V23" s="111"/>
-      <c r="W23" s="111"/>
-      <c r="X23" s="111"/>
-      <c r="Y23" s="111"/>
-      <c r="Z23" s="111"/>
-      <c r="AA23" s="111"/>
-      <c r="AB23" s="111"/>
-      <c r="AC23" s="111"/>
-      <c r="AD23" s="111"/>
-      <c r="AE23" s="111"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="128"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="128"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="128"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="128"/>
+      <c r="Q23" s="128"/>
+      <c r="R23" s="128"/>
+      <c r="S23" s="128"/>
+      <c r="T23" s="128"/>
+      <c r="U23" s="128"/>
+      <c r="V23" s="128"/>
+      <c r="W23" s="128"/>
+      <c r="X23" s="128"/>
+      <c r="Y23" s="128"/>
+      <c r="Z23" s="128"/>
+      <c r="AA23" s="128"/>
+      <c r="AB23" s="128"/>
+      <c r="AC23" s="128"/>
+      <c r="AD23" s="128"/>
+      <c r="AE23" s="128"/>
       <c r="AF23" s="132"/>
     </row>
     <row r="24" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -34196,7 +34196,7 @@
       <c r="AF26" s="75"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="55">
@@ -34325,7 +34325,7 @@
       </c>
     </row>
     <row r="28" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="117"/>
+      <c r="A28" s="115"/>
       <c r="B28" s="30">
         <f>B2</f>
         <v>46023</v>
@@ -34671,36 +34671,36 @@
       <c r="A35" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="111"/>
-      <c r="S35" s="111"/>
-      <c r="T35" s="111"/>
-      <c r="U35" s="111"/>
-      <c r="V35" s="111"/>
-      <c r="W35" s="111"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="111"/>
-      <c r="AA35" s="111"/>
-      <c r="AB35" s="111"/>
-      <c r="AC35" s="111"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="128"/>
+      <c r="S35" s="128"/>
+      <c r="T35" s="128"/>
+      <c r="U35" s="128"/>
+      <c r="V35" s="128"/>
+      <c r="W35" s="128"/>
+      <c r="X35" s="128"/>
+      <c r="Y35" s="128"/>
+      <c r="Z35" s="128"/>
+      <c r="AA35" s="128"/>
+      <c r="AB35" s="128"/>
+      <c r="AC35" s="128"/>
       <c r="AF35" s="80"/>
     </row>
     <row r="36" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -34778,7 +34778,7 @@
       <c r="AF38" s="75"/>
     </row>
     <row r="39" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="54">
@@ -34907,7 +34907,7 @@
       </c>
     </row>
     <row r="40" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="119"/>
+      <c r="A40" s="117"/>
       <c r="B40" s="30">
         <f>B2</f>
         <v>46023</v>
@@ -35253,36 +35253,36 @@
       <c r="A47" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="110" t="s">
+      <c r="B47" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
-      <c r="M47" s="111"/>
-      <c r="N47" s="111"/>
-      <c r="O47" s="111"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
-      <c r="R47" s="111"/>
-      <c r="S47" s="111"/>
-      <c r="T47" s="111"/>
-      <c r="U47" s="111"/>
-      <c r="V47" s="111"/>
-      <c r="W47" s="111"/>
-      <c r="X47" s="111"/>
-      <c r="Y47" s="111"/>
-      <c r="Z47" s="111"/>
-      <c r="AA47" s="111"/>
-      <c r="AB47" s="111"/>
-      <c r="AC47" s="111"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="128"/>
+      <c r="O47" s="128"/>
+      <c r="P47" s="128"/>
+      <c r="Q47" s="128"/>
+      <c r="R47" s="128"/>
+      <c r="S47" s="128"/>
+      <c r="T47" s="128"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="128"/>
+      <c r="W47" s="128"/>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="128"/>
+      <c r="Z47" s="128"/>
+      <c r="AA47" s="128"/>
+      <c r="AB47" s="128"/>
+      <c r="AC47" s="128"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="80"/>
@@ -35413,7 +35413,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -35530,7 +35530,7 @@
       </c>
     </row>
     <row r="2" spans="1:29" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>46054</v>
       </c>
@@ -35942,7 +35942,7 @@
       <c r="A12" s="74"/>
     </row>
     <row r="13" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -36059,7 +36059,7 @@
       </c>
     </row>
     <row r="14" spans="1:29" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>46054</v>
@@ -36441,36 +36441,36 @@
       <c r="A23" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="110" t="s">
+      <c r="B23" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="111"/>
-      <c r="N23" s="111"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="111"/>
-      <c r="S23" s="111"/>
-      <c r="T23" s="111"/>
-      <c r="U23" s="111"/>
-      <c r="V23" s="111"/>
-      <c r="W23" s="111"/>
-      <c r="X23" s="111"/>
-      <c r="Y23" s="111"/>
-      <c r="Z23" s="111"/>
-      <c r="AA23" s="111"/>
-      <c r="AB23" s="111"/>
-      <c r="AC23" s="111"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="128"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="128"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="128"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="128"/>
+      <c r="Q23" s="128"/>
+      <c r="R23" s="128"/>
+      <c r="S23" s="128"/>
+      <c r="T23" s="128"/>
+      <c r="U23" s="128"/>
+      <c r="V23" s="128"/>
+      <c r="W23" s="128"/>
+      <c r="X23" s="128"/>
+      <c r="Y23" s="128"/>
+      <c r="Z23" s="128"/>
+      <c r="AA23" s="128"/>
+      <c r="AB23" s="128"/>
+      <c r="AC23" s="128"/>
     </row>
     <row r="24" spans="1:29" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="70" t="s">
@@ -36542,7 +36542,7 @@
       <c r="A26" s="74"/>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="55">
@@ -36659,7 +36659,7 @@
       </c>
     </row>
     <row r="28" spans="1:29" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="117"/>
+      <c r="A28" s="115"/>
       <c r="B28" s="30">
         <f>B2</f>
         <v>46054</v>
@@ -36975,36 +36975,36 @@
       <c r="A35" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="111"/>
-      <c r="S35" s="111"/>
-      <c r="T35" s="111"/>
-      <c r="U35" s="111"/>
-      <c r="V35" s="111"/>
-      <c r="W35" s="111"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="111"/>
-      <c r="AA35" s="111"/>
-      <c r="AB35" s="111"/>
-      <c r="AC35" s="111"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="128"/>
+      <c r="S35" s="128"/>
+      <c r="T35" s="128"/>
+      <c r="U35" s="128"/>
+      <c r="V35" s="128"/>
+      <c r="W35" s="128"/>
+      <c r="X35" s="128"/>
+      <c r="Y35" s="128"/>
+      <c r="Z35" s="128"/>
+      <c r="AA35" s="128"/>
+      <c r="AB35" s="128"/>
+      <c r="AC35" s="128"/>
     </row>
     <row r="36" spans="1:29" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="70" t="s">
@@ -37074,7 +37074,7 @@
       <c r="A38" s="74"/>
     </row>
     <row r="39" spans="1:29" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="54">
@@ -37191,7 +37191,7 @@
       </c>
     </row>
     <row r="40" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="119"/>
+      <c r="A40" s="117"/>
       <c r="B40" s="30">
         <f>B2</f>
         <v>46054</v>
@@ -37507,36 +37507,36 @@
       <c r="A47" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="110" t="s">
+      <c r="B47" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
-      <c r="M47" s="111"/>
-      <c r="N47" s="111"/>
-      <c r="O47" s="111"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
-      <c r="R47" s="111"/>
-      <c r="S47" s="111"/>
-      <c r="T47" s="111"/>
-      <c r="U47" s="111"/>
-      <c r="V47" s="111"/>
-      <c r="W47" s="111"/>
-      <c r="X47" s="111"/>
-      <c r="Y47" s="111"/>
-      <c r="Z47" s="111"/>
-      <c r="AA47" s="111"/>
-      <c r="AB47" s="111"/>
-      <c r="AC47" s="111"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="128"/>
+      <c r="O47" s="128"/>
+      <c r="P47" s="128"/>
+      <c r="Q47" s="128"/>
+      <c r="R47" s="128"/>
+      <c r="S47" s="128"/>
+      <c r="T47" s="128"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="128"/>
+      <c r="W47" s="128"/>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="128"/>
+      <c r="Z47" s="128"/>
+      <c r="AA47" s="128"/>
+      <c r="AB47" s="128"/>
+      <c r="AC47" s="128"/>
     </row>
     <row r="48" spans="1:29" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="70" t="s">
@@ -37657,7 +37657,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -37782,7 +37782,7 @@
       </c>
     </row>
     <row r="2" spans="1:31" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>46113</v>
       </c>
@@ -38220,7 +38220,7 @@
       <c r="A12" s="74"/>
     </row>
     <row r="13" spans="1:31" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -38345,7 +38345,7 @@
       </c>
     </row>
     <row r="14" spans="1:31" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>46113</v>
@@ -38854,7 +38854,7 @@
       <c r="A26" s="74"/>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="55">
@@ -38979,7 +38979,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="117"/>
+      <c r="A28" s="115"/>
       <c r="B28" s="30">
         <f>B2</f>
         <v>46113</v>
@@ -39315,34 +39315,34 @@
       <c r="A35" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="110"/>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="111"/>
-      <c r="S35" s="111"/>
-      <c r="T35" s="111"/>
-      <c r="U35" s="111"/>
-      <c r="V35" s="111"/>
-      <c r="W35" s="111"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="111"/>
-      <c r="AA35" s="111"/>
-      <c r="AB35" s="111"/>
-      <c r="AC35" s="111"/>
+      <c r="B35" s="127"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="128"/>
+      <c r="S35" s="128"/>
+      <c r="T35" s="128"/>
+      <c r="U35" s="128"/>
+      <c r="V35" s="128"/>
+      <c r="W35" s="128"/>
+      <c r="X35" s="128"/>
+      <c r="Y35" s="128"/>
+      <c r="Z35" s="128"/>
+      <c r="AA35" s="128"/>
+      <c r="AB35" s="128"/>
+      <c r="AC35" s="128"/>
     </row>
     <row r="36" spans="1:31" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="70" t="s">
@@ -39416,7 +39416,7 @@
       <c r="A38" s="74"/>
     </row>
     <row r="39" spans="1:31" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="54">
@@ -39541,7 +39541,7 @@
       </c>
     </row>
     <row r="40" spans="1:31" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="119"/>
+      <c r="A40" s="117"/>
       <c r="B40" s="30">
         <f>B2</f>
         <v>46113</v>
@@ -39877,36 +39877,36 @@
       <c r="A47" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="110" t="s">
+      <c r="B47" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
-      <c r="M47" s="111"/>
-      <c r="N47" s="111"/>
-      <c r="O47" s="111"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
-      <c r="R47" s="111"/>
-      <c r="S47" s="111"/>
-      <c r="T47" s="111"/>
-      <c r="U47" s="111"/>
-      <c r="V47" s="111"/>
-      <c r="W47" s="111"/>
-      <c r="X47" s="111"/>
-      <c r="Y47" s="111"/>
-      <c r="Z47" s="111"/>
-      <c r="AA47" s="111"/>
-      <c r="AB47" s="111"/>
-      <c r="AC47" s="111"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="128"/>
+      <c r="O47" s="128"/>
+      <c r="P47" s="128"/>
+      <c r="Q47" s="128"/>
+      <c r="R47" s="128"/>
+      <c r="S47" s="128"/>
+      <c r="T47" s="128"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="128"/>
+      <c r="W47" s="128"/>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="128"/>
+      <c r="Z47" s="128"/>
+      <c r="AA47" s="128"/>
+      <c r="AB47" s="128"/>
+      <c r="AC47" s="128"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
     </row>
@@ -40026,7 +40026,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -40075,7 +40075,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>46143</v>
       </c>
@@ -40266,7 +40266,7 @@
       <c r="A12" s="74"/>
     </row>
     <row r="13" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -40315,7 +40315,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>46143</v>
@@ -40539,7 +40539,7 @@
       <c r="A26" s="74"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="55">
@@ -40588,7 +40588,7 @@
       </c>
     </row>
     <row r="28" spans="1:12" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="117"/>
+      <c r="A28" s="115"/>
       <c r="B28" s="30">
         <f>B2</f>
         <v>46143</v>
@@ -40734,19 +40734,19 @@
       <c r="A35" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
     </row>
     <row r="36" spans="1:12" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="70" t="s">
@@ -40782,7 +40782,7 @@
       <c r="A38" s="74"/>
     </row>
     <row r="39" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="54">
@@ -40831,7 +40831,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="119"/>
+      <c r="A40" s="117"/>
       <c r="B40" s="30">
         <f>B2</f>
         <v>46143</v>
@@ -40977,19 +40977,19 @@
       <c r="A47" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="110" t="s">
+      <c r="B47" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
     </row>
     <row r="48" spans="1:12" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="70" t="s">
@@ -41076,7 +41076,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -41201,7 +41201,7 @@
       </c>
     </row>
     <row r="2" spans="1:31" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>46174</v>
       </c>
@@ -41639,7 +41639,7 @@
       <c r="A12" s="74"/>
     </row>
     <row r="13" spans="1:31" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -41764,7 +41764,7 @@
       </c>
     </row>
     <row r="14" spans="1:31" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>46174</v>
@@ -42273,7 +42273,7 @@
       <c r="A26" s="74"/>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="55">
@@ -42398,7 +42398,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="117"/>
+      <c r="A28" s="115"/>
       <c r="B28" s="30">
         <f>B2</f>
         <v>46174</v>
@@ -42734,34 +42734,34 @@
       <c r="A35" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="110"/>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="111"/>
-      <c r="S35" s="111"/>
-      <c r="T35" s="111"/>
-      <c r="U35" s="111"/>
-      <c r="V35" s="111"/>
-      <c r="W35" s="111"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="111"/>
-      <c r="AA35" s="111"/>
-      <c r="AB35" s="111"/>
-      <c r="AC35" s="111"/>
+      <c r="B35" s="127"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="128"/>
+      <c r="S35" s="128"/>
+      <c r="T35" s="128"/>
+      <c r="U35" s="128"/>
+      <c r="V35" s="128"/>
+      <c r="W35" s="128"/>
+      <c r="X35" s="128"/>
+      <c r="Y35" s="128"/>
+      <c r="Z35" s="128"/>
+      <c r="AA35" s="128"/>
+      <c r="AB35" s="128"/>
+      <c r="AC35" s="128"/>
     </row>
     <row r="36" spans="1:31" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="70" t="s">
@@ -42835,7 +42835,7 @@
       <c r="A38" s="74"/>
     </row>
     <row r="39" spans="1:31" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="54">
@@ -42960,7 +42960,7 @@
       </c>
     </row>
     <row r="40" spans="1:31" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="119"/>
+      <c r="A40" s="117"/>
       <c r="B40" s="30">
         <f>B2</f>
         <v>46174</v>
@@ -43296,36 +43296,36 @@
       <c r="A47" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="110" t="s">
+      <c r="B47" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
-      <c r="M47" s="111"/>
-      <c r="N47" s="111"/>
-      <c r="O47" s="111"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
-      <c r="R47" s="111"/>
-      <c r="S47" s="111"/>
-      <c r="T47" s="111"/>
-      <c r="U47" s="111"/>
-      <c r="V47" s="111"/>
-      <c r="W47" s="111"/>
-      <c r="X47" s="111"/>
-      <c r="Y47" s="111"/>
-      <c r="Z47" s="111"/>
-      <c r="AA47" s="111"/>
-      <c r="AB47" s="111"/>
-      <c r="AC47" s="111"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="128"/>
+      <c r="O47" s="128"/>
+      <c r="P47" s="128"/>
+      <c r="Q47" s="128"/>
+      <c r="R47" s="128"/>
+      <c r="S47" s="128"/>
+      <c r="T47" s="128"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="128"/>
+      <c r="W47" s="128"/>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="128"/>
+      <c r="Z47" s="128"/>
+      <c r="AA47" s="128"/>
+      <c r="AB47" s="128"/>
+      <c r="AC47" s="128"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
     </row>
@@ -43451,7 +43451,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="62">
@@ -43580,7 +43580,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>46204</v>
       </c>
@@ -44031,7 +44031,7 @@
       <c r="A12" s="74"/>
     </row>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -44160,7 +44160,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>46204</v>
@@ -44684,7 +44684,7 @@
       <c r="A26" s="74"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="55">
@@ -44813,7 +44813,7 @@
       </c>
     </row>
     <row r="28" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="117"/>
+      <c r="A28" s="115"/>
       <c r="B28" s="30">
         <f>B2</f>
         <v>46204</v>
@@ -45159,34 +45159,34 @@
       <c r="A35" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="110"/>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="111"/>
-      <c r="S35" s="111"/>
-      <c r="T35" s="111"/>
-      <c r="U35" s="111"/>
-      <c r="V35" s="111"/>
-      <c r="W35" s="111"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="111"/>
-      <c r="AA35" s="111"/>
-      <c r="AB35" s="111"/>
-      <c r="AC35" s="111"/>
+      <c r="B35" s="127"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="128"/>
+      <c r="S35" s="128"/>
+      <c r="T35" s="128"/>
+      <c r="U35" s="128"/>
+      <c r="V35" s="128"/>
+      <c r="W35" s="128"/>
+      <c r="X35" s="128"/>
+      <c r="Y35" s="128"/>
+      <c r="Z35" s="128"/>
+      <c r="AA35" s="128"/>
+      <c r="AB35" s="128"/>
+      <c r="AC35" s="128"/>
     </row>
     <row r="36" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="70" t="s">
@@ -45262,7 +45262,7 @@
       <c r="A38" s="74"/>
     </row>
     <row r="39" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="54">
@@ -45391,7 +45391,7 @@
       </c>
     </row>
     <row r="40" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="119"/>
+      <c r="A40" s="117"/>
       <c r="B40" s="30">
         <f>B2</f>
         <v>46204</v>
@@ -45737,36 +45737,36 @@
       <c r="A47" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="110" t="s">
+      <c r="B47" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
-      <c r="M47" s="111"/>
-      <c r="N47" s="111"/>
-      <c r="O47" s="111"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
-      <c r="R47" s="111"/>
-      <c r="S47" s="111"/>
-      <c r="T47" s="111"/>
-      <c r="U47" s="111"/>
-      <c r="V47" s="111"/>
-      <c r="W47" s="111"/>
-      <c r="X47" s="111"/>
-      <c r="Y47" s="111"/>
-      <c r="Z47" s="111"/>
-      <c r="AA47" s="111"/>
-      <c r="AB47" s="111"/>
-      <c r="AC47" s="111"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="128"/>
+      <c r="O47" s="128"/>
+      <c r="P47" s="128"/>
+      <c r="Q47" s="128"/>
+      <c r="R47" s="128"/>
+      <c r="S47" s="128"/>
+      <c r="T47" s="128"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="128"/>
+      <c r="W47" s="128"/>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="128"/>
+      <c r="Z47" s="128"/>
+      <c r="AA47" s="128"/>
+      <c r="AB47" s="128"/>
+      <c r="AC47" s="128"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
@@ -45880,23 +45880,14 @@
   <dimension ref="A1:AF8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="54.140625" style="1" customWidth="1"/>
-    <col min="2" max="5" width="10" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="11" width="8.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="15" width="8.28515625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.28515625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" style="1" customWidth="1"/>
-    <col min="18" max="25" width="9.28515625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" style="1" customWidth="1"/>
-    <col min="27" max="27" width="9.28515625" style="1" customWidth="1"/>
-    <col min="28" max="31" width="9.140625" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="32" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>59</v>
       </c>
       <c r="B1" s="62">
@@ -46025,7 +46016,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>46235</v>
       </c>
@@ -46156,8 +46147,8 @@
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -46237,7 +46228,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -46335,7 +46326,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45170</v>
       </c>
@@ -46784,7 +46775,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -46882,7 +46873,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="13">
         <v>45170</v>
       </c>
@@ -47410,7 +47401,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -47508,7 +47499,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="13">
         <v>45170</v>
       </c>
@@ -47929,7 +47920,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -48027,7 +48018,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="17">
         <v>45170</v>
       </c>
@@ -48487,7 +48478,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -48585,7 +48576,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45200</v>
       </c>
@@ -48956,13 +48947,13 @@
       <c r="Y9" s="24"/>
       <c r="Z9" s="42"/>
       <c r="AA9" s="42"/>
-      <c r="AB9" s="120" t="s">
+      <c r="AB9" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="AC9" s="121"/>
-      <c r="AD9" s="121"/>
-      <c r="AE9" s="121"/>
-      <c r="AF9" s="122"/>
+      <c r="AC9" s="119"/>
+      <c r="AD9" s="119"/>
+      <c r="AE9" s="119"/>
+      <c r="AF9" s="120"/>
     </row>
     <row r="10" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
@@ -49036,7 +49027,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -49134,7 +49125,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="13">
         <v>45200</v>
       </c>
@@ -49583,13 +49574,13 @@
       <c r="Y24" s="35"/>
       <c r="Z24" s="35"/>
       <c r="AA24" s="35"/>
-      <c r="AB24" s="120" t="s">
+      <c r="AB24" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="AC24" s="121"/>
-      <c r="AD24" s="121"/>
-      <c r="AE24" s="121"/>
-      <c r="AF24" s="122"/>
+      <c r="AC24" s="119"/>
+      <c r="AD24" s="119"/>
+      <c r="AE24" s="119"/>
+      <c r="AF24" s="120"/>
     </row>
     <row r="25" spans="1:34" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
@@ -49663,7 +49654,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -49761,7 +49752,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="13">
         <v>45200</v>
       </c>
@@ -50104,13 +50095,13 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="35"/>
       <c r="AA36" s="35"/>
-      <c r="AB36" s="120" t="s">
+      <c r="AB36" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="AC36" s="121"/>
-      <c r="AD36" s="121"/>
-      <c r="AE36" s="121"/>
-      <c r="AF36" s="122"/>
+      <c r="AC36" s="119"/>
+      <c r="AD36" s="119"/>
+      <c r="AE36" s="119"/>
+      <c r="AF36" s="120"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -50184,7 +50175,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -50282,7 +50273,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="17">
         <v>45200</v>
       </c>
@@ -50623,13 +50614,13 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
       <c r="AA48" s="35"/>
-      <c r="AB48" s="120" t="s">
+      <c r="AB48" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="AC48" s="121"/>
-      <c r="AD48" s="121"/>
-      <c r="AE48" s="121"/>
-      <c r="AF48" s="122"/>
+      <c r="AC48" s="119"/>
+      <c r="AD48" s="119"/>
+      <c r="AE48" s="119"/>
+      <c r="AF48" s="120"/>
     </row>
     <row r="49" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -50758,7 +50749,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -50856,7 +50847,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45261</v>
       </c>
@@ -51201,39 +51192,39 @@
       <c r="A9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="121"/>
-      <c r="K9" s="121"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
-      <c r="Q9" s="121"/>
-      <c r="R9" s="121"/>
-      <c r="S9" s="121"/>
-      <c r="T9" s="121"/>
-      <c r="U9" s="121"/>
-      <c r="V9" s="121"/>
-      <c r="W9" s="121"/>
-      <c r="X9" s="121"/>
-      <c r="Y9" s="121"/>
-      <c r="Z9" s="121"/>
-      <c r="AA9" s="121"/>
-      <c r="AB9" s="121"/>
-      <c r="AC9" s="121"/>
-      <c r="AD9" s="121"/>
-      <c r="AE9" s="121"/>
-      <c r="AF9" s="122"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="119"/>
+      <c r="R9" s="119"/>
+      <c r="S9" s="119"/>
+      <c r="T9" s="119"/>
+      <c r="U9" s="119"/>
+      <c r="V9" s="119"/>
+      <c r="W9" s="119"/>
+      <c r="X9" s="119"/>
+      <c r="Y9" s="119"/>
+      <c r="Z9" s="119"/>
+      <c r="AA9" s="119"/>
+      <c r="AB9" s="119"/>
+      <c r="AC9" s="119"/>
+      <c r="AD9" s="119"/>
+      <c r="AE9" s="119"/>
+      <c r="AF9" s="120"/>
     </row>
     <row r="10" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
@@ -51307,7 +51298,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -51405,7 +51396,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="13">
         <v>45261</v>
       </c>
@@ -51932,7 +51923,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -52030,7 +52021,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="13">
         <v>45261</v>
       </c>
@@ -52347,39 +52338,39 @@
       <c r="A36" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="120" t="s">
+      <c r="B36" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="121"/>
-      <c r="D36" s="121"/>
-      <c r="E36" s="121"/>
-      <c r="F36" s="121"/>
-      <c r="G36" s="121"/>
-      <c r="H36" s="121"/>
-      <c r="I36" s="121"/>
-      <c r="J36" s="121"/>
-      <c r="K36" s="121"/>
-      <c r="L36" s="121"/>
-      <c r="M36" s="121"/>
-      <c r="N36" s="121"/>
-      <c r="O36" s="121"/>
-      <c r="P36" s="121"/>
-      <c r="Q36" s="121"/>
-      <c r="R36" s="121"/>
-      <c r="S36" s="121"/>
-      <c r="T36" s="121"/>
-      <c r="U36" s="121"/>
-      <c r="V36" s="121"/>
-      <c r="W36" s="121"/>
-      <c r="X36" s="121"/>
-      <c r="Y36" s="121"/>
-      <c r="Z36" s="121"/>
-      <c r="AA36" s="121"/>
-      <c r="AB36" s="121"/>
-      <c r="AC36" s="121"/>
-      <c r="AD36" s="121"/>
-      <c r="AE36" s="121"/>
-      <c r="AF36" s="122"/>
+      <c r="C36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="119"/>
+      <c r="H36" s="119"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="119"/>
+      <c r="K36" s="119"/>
+      <c r="L36" s="119"/>
+      <c r="M36" s="119"/>
+      <c r="N36" s="119"/>
+      <c r="O36" s="119"/>
+      <c r="P36" s="119"/>
+      <c r="Q36" s="119"/>
+      <c r="R36" s="119"/>
+      <c r="S36" s="119"/>
+      <c r="T36" s="119"/>
+      <c r="U36" s="119"/>
+      <c r="V36" s="119"/>
+      <c r="W36" s="119"/>
+      <c r="X36" s="119"/>
+      <c r="Y36" s="119"/>
+      <c r="Z36" s="119"/>
+      <c r="AA36" s="119"/>
+      <c r="AB36" s="119"/>
+      <c r="AC36" s="119"/>
+      <c r="AD36" s="119"/>
+      <c r="AE36" s="119"/>
+      <c r="AF36" s="120"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -52453,7 +52444,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -52551,7 +52542,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="17">
         <v>45261</v>
       </c>
@@ -52866,39 +52857,39 @@
       <c r="A48" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="120" t="s">
+      <c r="B48" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="C48" s="121"/>
-      <c r="D48" s="121"/>
-      <c r="E48" s="121"/>
-      <c r="F48" s="121"/>
-      <c r="G48" s="121"/>
-      <c r="H48" s="121"/>
-      <c r="I48" s="121"/>
-      <c r="J48" s="121"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="121"/>
-      <c r="P48" s="121"/>
-      <c r="Q48" s="121"/>
-      <c r="R48" s="121"/>
-      <c r="S48" s="121"/>
-      <c r="T48" s="121"/>
-      <c r="U48" s="121"/>
-      <c r="V48" s="121"/>
-      <c r="W48" s="121"/>
-      <c r="X48" s="121"/>
-      <c r="Y48" s="121"/>
-      <c r="Z48" s="121"/>
-      <c r="AA48" s="121"/>
-      <c r="AB48" s="121"/>
-      <c r="AC48" s="121"/>
-      <c r="AD48" s="121"/>
-      <c r="AE48" s="121"/>
-      <c r="AF48" s="122"/>
+      <c r="C48" s="119"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="119"/>
+      <c r="F48" s="119"/>
+      <c r="G48" s="119"/>
+      <c r="H48" s="119"/>
+      <c r="I48" s="119"/>
+      <c r="J48" s="119"/>
+      <c r="K48" s="119"/>
+      <c r="L48" s="119"/>
+      <c r="M48" s="119"/>
+      <c r="N48" s="119"/>
+      <c r="O48" s="119"/>
+      <c r="P48" s="119"/>
+      <c r="Q48" s="119"/>
+      <c r="R48" s="119"/>
+      <c r="S48" s="119"/>
+      <c r="T48" s="119"/>
+      <c r="U48" s="119"/>
+      <c r="V48" s="119"/>
+      <c r="W48" s="119"/>
+      <c r="X48" s="119"/>
+      <c r="Y48" s="119"/>
+      <c r="Z48" s="119"/>
+      <c r="AA48" s="119"/>
+      <c r="AB48" s="119"/>
+      <c r="AC48" s="119"/>
+      <c r="AD48" s="119"/>
+      <c r="AE48" s="119"/>
+      <c r="AF48" s="120"/>
     </row>
     <row r="49" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -53018,7 +53009,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -53116,7 +53107,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45292</v>
       </c>
@@ -53461,39 +53452,39 @@
       <c r="A9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="121"/>
-      <c r="K9" s="121"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
-      <c r="Q9" s="121"/>
-      <c r="R9" s="121"/>
-      <c r="S9" s="121"/>
-      <c r="T9" s="121"/>
-      <c r="U9" s="121"/>
-      <c r="V9" s="121"/>
-      <c r="W9" s="121"/>
-      <c r="X9" s="121"/>
-      <c r="Y9" s="121"/>
-      <c r="Z9" s="121"/>
-      <c r="AA9" s="121"/>
-      <c r="AB9" s="121"/>
-      <c r="AC9" s="121"/>
-      <c r="AD9" s="121"/>
-      <c r="AE9" s="121"/>
-      <c r="AF9" s="122"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="119"/>
+      <c r="R9" s="119"/>
+      <c r="S9" s="119"/>
+      <c r="T9" s="119"/>
+      <c r="U9" s="119"/>
+      <c r="V9" s="119"/>
+      <c r="W9" s="119"/>
+      <c r="X9" s="119"/>
+      <c r="Y9" s="119"/>
+      <c r="Z9" s="119"/>
+      <c r="AA9" s="119"/>
+      <c r="AB9" s="119"/>
+      <c r="AC9" s="119"/>
+      <c r="AD9" s="119"/>
+      <c r="AE9" s="119"/>
+      <c r="AF9" s="120"/>
     </row>
     <row r="10" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
@@ -53567,7 +53558,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -53665,7 +53656,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="13">
         <v>45292</v>
       </c>
@@ -54191,7 +54182,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -54289,7 +54280,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="13">
         <v>45292</v>
       </c>
@@ -54606,39 +54597,39 @@
       <c r="A36" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="120" t="s">
+      <c r="B36" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="121"/>
-      <c r="D36" s="121"/>
-      <c r="E36" s="121"/>
-      <c r="F36" s="121"/>
-      <c r="G36" s="121"/>
-      <c r="H36" s="121"/>
-      <c r="I36" s="121"/>
-      <c r="J36" s="121"/>
-      <c r="K36" s="121"/>
-      <c r="L36" s="121"/>
-      <c r="M36" s="121"/>
-      <c r="N36" s="121"/>
-      <c r="O36" s="121"/>
-      <c r="P36" s="121"/>
-      <c r="Q36" s="121"/>
-      <c r="R36" s="121"/>
-      <c r="S36" s="121"/>
-      <c r="T36" s="121"/>
-      <c r="U36" s="121"/>
-      <c r="V36" s="121"/>
-      <c r="W36" s="121"/>
-      <c r="X36" s="121"/>
-      <c r="Y36" s="121"/>
-      <c r="Z36" s="121"/>
-      <c r="AA36" s="121"/>
-      <c r="AB36" s="121"/>
-      <c r="AC36" s="121"/>
-      <c r="AD36" s="121"/>
-      <c r="AE36" s="121"/>
-      <c r="AF36" s="122"/>
+      <c r="C36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="119"/>
+      <c r="H36" s="119"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="119"/>
+      <c r="K36" s="119"/>
+      <c r="L36" s="119"/>
+      <c r="M36" s="119"/>
+      <c r="N36" s="119"/>
+      <c r="O36" s="119"/>
+      <c r="P36" s="119"/>
+      <c r="Q36" s="119"/>
+      <c r="R36" s="119"/>
+      <c r="S36" s="119"/>
+      <c r="T36" s="119"/>
+      <c r="U36" s="119"/>
+      <c r="V36" s="119"/>
+      <c r="W36" s="119"/>
+      <c r="X36" s="119"/>
+      <c r="Y36" s="119"/>
+      <c r="Z36" s="119"/>
+      <c r="AA36" s="119"/>
+      <c r="AB36" s="119"/>
+      <c r="AC36" s="119"/>
+      <c r="AD36" s="119"/>
+      <c r="AE36" s="119"/>
+      <c r="AF36" s="120"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -54712,7 +54703,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -54810,7 +54801,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="13">
         <v>45292</v>
       </c>
@@ -55125,39 +55116,39 @@
       <c r="A48" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="120" t="s">
+      <c r="B48" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="C48" s="121"/>
-      <c r="D48" s="121"/>
-      <c r="E48" s="121"/>
-      <c r="F48" s="121"/>
-      <c r="G48" s="121"/>
-      <c r="H48" s="121"/>
-      <c r="I48" s="121"/>
-      <c r="J48" s="121"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="121"/>
-      <c r="P48" s="121"/>
-      <c r="Q48" s="121"/>
-      <c r="R48" s="121"/>
-      <c r="S48" s="121"/>
-      <c r="T48" s="121"/>
-      <c r="U48" s="121"/>
-      <c r="V48" s="121"/>
-      <c r="W48" s="121"/>
-      <c r="X48" s="121"/>
-      <c r="Y48" s="121"/>
-      <c r="Z48" s="121"/>
-      <c r="AA48" s="121"/>
-      <c r="AB48" s="121"/>
-      <c r="AC48" s="121"/>
-      <c r="AD48" s="121"/>
-      <c r="AE48" s="121"/>
-      <c r="AF48" s="122"/>
+      <c r="C48" s="119"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="119"/>
+      <c r="F48" s="119"/>
+      <c r="G48" s="119"/>
+      <c r="H48" s="119"/>
+      <c r="I48" s="119"/>
+      <c r="J48" s="119"/>
+      <c r="K48" s="119"/>
+      <c r="L48" s="119"/>
+      <c r="M48" s="119"/>
+      <c r="N48" s="119"/>
+      <c r="O48" s="119"/>
+      <c r="P48" s="119"/>
+      <c r="Q48" s="119"/>
+      <c r="R48" s="119"/>
+      <c r="S48" s="119"/>
+      <c r="T48" s="119"/>
+      <c r="U48" s="119"/>
+      <c r="V48" s="119"/>
+      <c r="W48" s="119"/>
+      <c r="X48" s="119"/>
+      <c r="Y48" s="119"/>
+      <c r="Z48" s="119"/>
+      <c r="AA48" s="119"/>
+      <c r="AB48" s="119"/>
+      <c r="AC48" s="119"/>
+      <c r="AD48" s="119"/>
+      <c r="AE48" s="119"/>
+      <c r="AF48" s="120"/>
     </row>
     <row r="49" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -55276,7 +55267,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -55370,7 +55361,7 @@
       <c r="AF1" s="11"/>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45323</v>
       </c>
@@ -55709,39 +55700,39 @@
       <c r="A9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="121"/>
-      <c r="K9" s="121"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
-      <c r="Q9" s="121"/>
-      <c r="R9" s="121"/>
-      <c r="S9" s="121"/>
-      <c r="T9" s="121"/>
-      <c r="U9" s="121"/>
-      <c r="V9" s="121"/>
-      <c r="W9" s="121"/>
-      <c r="X9" s="121"/>
-      <c r="Y9" s="121"/>
-      <c r="Z9" s="121"/>
-      <c r="AA9" s="121"/>
-      <c r="AB9" s="121"/>
-      <c r="AC9" s="121"/>
-      <c r="AD9" s="121"/>
-      <c r="AE9" s="121"/>
-      <c r="AF9" s="122"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="119"/>
+      <c r="R9" s="119"/>
+      <c r="S9" s="119"/>
+      <c r="T9" s="119"/>
+      <c r="U9" s="119"/>
+      <c r="V9" s="119"/>
+      <c r="W9" s="119"/>
+      <c r="X9" s="119"/>
+      <c r="Y9" s="119"/>
+      <c r="Z9" s="119"/>
+      <c r="AA9" s="119"/>
+      <c r="AB9" s="119"/>
+      <c r="AC9" s="119"/>
+      <c r="AD9" s="119"/>
+      <c r="AE9" s="119"/>
+      <c r="AF9" s="120"/>
     </row>
     <row r="10" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
@@ -55815,7 +55806,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -55909,7 +55900,7 @@
       <c r="AF13" s="14"/>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="13">
         <f>B2</f>
         <v>45323</v>
@@ -56461,7 +56452,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -56555,7 +56546,7 @@
       <c r="AF28" s="8"/>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="13">
         <f>B2</f>
         <v>45323</v>
@@ -56897,39 +56888,39 @@
       <c r="A36" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="120" t="s">
+      <c r="B36" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="121"/>
-      <c r="D36" s="121"/>
-      <c r="E36" s="121"/>
-      <c r="F36" s="121"/>
-      <c r="G36" s="121"/>
-      <c r="H36" s="121"/>
-      <c r="I36" s="121"/>
-      <c r="J36" s="121"/>
-      <c r="K36" s="121"/>
-      <c r="L36" s="121"/>
-      <c r="M36" s="121"/>
-      <c r="N36" s="121"/>
-      <c r="O36" s="121"/>
-      <c r="P36" s="121"/>
-      <c r="Q36" s="121"/>
-      <c r="R36" s="121"/>
-      <c r="S36" s="121"/>
-      <c r="T36" s="121"/>
-      <c r="U36" s="121"/>
-      <c r="V36" s="121"/>
-      <c r="W36" s="121"/>
-      <c r="X36" s="121"/>
-      <c r="Y36" s="121"/>
-      <c r="Z36" s="121"/>
-      <c r="AA36" s="121"/>
-      <c r="AB36" s="121"/>
-      <c r="AC36" s="121"/>
-      <c r="AD36" s="121"/>
-      <c r="AE36" s="121"/>
-      <c r="AF36" s="122"/>
+      <c r="C36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="119"/>
+      <c r="H36" s="119"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="119"/>
+      <c r="K36" s="119"/>
+      <c r="L36" s="119"/>
+      <c r="M36" s="119"/>
+      <c r="N36" s="119"/>
+      <c r="O36" s="119"/>
+      <c r="P36" s="119"/>
+      <c r="Q36" s="119"/>
+      <c r="R36" s="119"/>
+      <c r="S36" s="119"/>
+      <c r="T36" s="119"/>
+      <c r="U36" s="119"/>
+      <c r="V36" s="119"/>
+      <c r="W36" s="119"/>
+      <c r="X36" s="119"/>
+      <c r="Y36" s="119"/>
+      <c r="Z36" s="119"/>
+      <c r="AA36" s="119"/>
+      <c r="AB36" s="119"/>
+      <c r="AC36" s="119"/>
+      <c r="AD36" s="119"/>
+      <c r="AE36" s="119"/>
+      <c r="AF36" s="120"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -57003,7 +56994,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -57097,7 +57088,7 @@
       <c r="AF40" s="15"/>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="13">
         <f>B2</f>
         <v>45323</v>
@@ -57437,39 +57428,39 @@
       <c r="A48" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="120" t="s">
+      <c r="B48" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="C48" s="121"/>
-      <c r="D48" s="121"/>
-      <c r="E48" s="121"/>
-      <c r="F48" s="121"/>
-      <c r="G48" s="121"/>
-      <c r="H48" s="121"/>
-      <c r="I48" s="121"/>
-      <c r="J48" s="121"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="121"/>
-      <c r="P48" s="121"/>
-      <c r="Q48" s="121"/>
-      <c r="R48" s="121"/>
-      <c r="S48" s="121"/>
-      <c r="T48" s="121"/>
-      <c r="U48" s="121"/>
-      <c r="V48" s="121"/>
-      <c r="W48" s="121"/>
-      <c r="X48" s="121"/>
-      <c r="Y48" s="121"/>
-      <c r="Z48" s="121"/>
-      <c r="AA48" s="121"/>
-      <c r="AB48" s="121"/>
-      <c r="AC48" s="121"/>
-      <c r="AD48" s="121"/>
-      <c r="AE48" s="121"/>
-      <c r="AF48" s="122"/>
+      <c r="C48" s="119"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="119"/>
+      <c r="F48" s="119"/>
+      <c r="G48" s="119"/>
+      <c r="H48" s="119"/>
+      <c r="I48" s="119"/>
+      <c r="J48" s="119"/>
+      <c r="K48" s="119"/>
+      <c r="L48" s="119"/>
+      <c r="M48" s="119"/>
+      <c r="N48" s="119"/>
+      <c r="O48" s="119"/>
+      <c r="P48" s="119"/>
+      <c r="Q48" s="119"/>
+      <c r="R48" s="119"/>
+      <c r="S48" s="119"/>
+      <c r="T48" s="119"/>
+      <c r="U48" s="119"/>
+      <c r="V48" s="119"/>
+      <c r="W48" s="119"/>
+      <c r="X48" s="119"/>
+      <c r="Y48" s="119"/>
+      <c r="Z48" s="119"/>
+      <c r="AA48" s="119"/>
+      <c r="AB48" s="119"/>
+      <c r="AC48" s="119"/>
+      <c r="AD48" s="119"/>
+      <c r="AE48" s="119"/>
+      <c r="AF48" s="120"/>
     </row>
     <row r="49" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -57591,7 +57582,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="53">
@@ -57720,7 +57711,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45536</v>
       </c>
@@ -58173,7 +58164,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -58302,7 +58293,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45536</v>
@@ -58863,7 +58854,7 @@
     </row>
     <row r="27" spans="1:35" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -58992,7 +58983,7 @@
       </c>
     </row>
     <row r="29" spans="1:35" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45536</v>
@@ -59342,39 +59333,39 @@
       <c r="A36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="126" t="s">
+      <c r="B36" s="124" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="127"/>
-      <c r="D36" s="127"/>
-      <c r="E36" s="127"/>
-      <c r="F36" s="127"/>
-      <c r="G36" s="127"/>
-      <c r="H36" s="127"/>
-      <c r="I36" s="127"/>
-      <c r="J36" s="127"/>
-      <c r="K36" s="127"/>
-      <c r="L36" s="127"/>
-      <c r="M36" s="127"/>
-      <c r="N36" s="127"/>
-      <c r="O36" s="127"/>
-      <c r="P36" s="127"/>
-      <c r="Q36" s="127"/>
-      <c r="R36" s="127"/>
-      <c r="S36" s="127"/>
-      <c r="T36" s="127"/>
-      <c r="U36" s="127"/>
-      <c r="V36" s="127"/>
-      <c r="W36" s="127"/>
-      <c r="X36" s="127"/>
-      <c r="Y36" s="127"/>
-      <c r="Z36" s="127"/>
-      <c r="AA36" s="127"/>
-      <c r="AB36" s="127"/>
-      <c r="AC36" s="127"/>
-      <c r="AD36" s="127"/>
-      <c r="AE36" s="127"/>
-      <c r="AF36" s="128"/>
+      <c r="C36" s="125"/>
+      <c r="D36" s="125"/>
+      <c r="E36" s="125"/>
+      <c r="F36" s="125"/>
+      <c r="G36" s="125"/>
+      <c r="H36" s="125"/>
+      <c r="I36" s="125"/>
+      <c r="J36" s="125"/>
+      <c r="K36" s="125"/>
+      <c r="L36" s="125"/>
+      <c r="M36" s="125"/>
+      <c r="N36" s="125"/>
+      <c r="O36" s="125"/>
+      <c r="P36" s="125"/>
+      <c r="Q36" s="125"/>
+      <c r="R36" s="125"/>
+      <c r="S36" s="125"/>
+      <c r="T36" s="125"/>
+      <c r="U36" s="125"/>
+      <c r="V36" s="125"/>
+      <c r="W36" s="125"/>
+      <c r="X36" s="125"/>
+      <c r="Y36" s="125"/>
+      <c r="Z36" s="125"/>
+      <c r="AA36" s="125"/>
+      <c r="AB36" s="125"/>
+      <c r="AC36" s="125"/>
+      <c r="AD36" s="125"/>
+      <c r="AE36" s="125"/>
+      <c r="AF36" s="126"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -59448,7 +59439,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -59577,7 +59568,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45536</v>
@@ -59923,39 +59914,39 @@
       <c r="A48" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="123" t="s">
+      <c r="B48" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="124"/>
-      <c r="K48" s="124"/>
-      <c r="L48" s="124"/>
-      <c r="M48" s="124"/>
-      <c r="N48" s="124"/>
-      <c r="O48" s="124"/>
-      <c r="P48" s="124"/>
-      <c r="Q48" s="124"/>
-      <c r="R48" s="124"/>
-      <c r="S48" s="124"/>
-      <c r="T48" s="124"/>
-      <c r="U48" s="124"/>
-      <c r="V48" s="124"/>
-      <c r="W48" s="124"/>
-      <c r="X48" s="124"/>
-      <c r="Y48" s="124"/>
-      <c r="Z48" s="124"/>
-      <c r="AA48" s="124"/>
-      <c r="AB48" s="124"/>
-      <c r="AC48" s="124"/>
-      <c r="AD48" s="124"/>
-      <c r="AE48" s="124"/>
-      <c r="AF48" s="125"/>
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="122"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="122"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="122"/>
+      <c r="S48" s="122"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="122"/>
+      <c r="V48" s="122"/>
+      <c r="W48" s="122"/>
+      <c r="X48" s="122"/>
+      <c r="Y48" s="122"/>
+      <c r="Z48" s="122"/>
+      <c r="AA48" s="122"/>
+      <c r="AB48" s="122"/>
+      <c r="AC48" s="122"/>
+      <c r="AD48" s="122"/>
+      <c r="AE48" s="122"/>
+      <c r="AF48" s="123"/>
     </row>
     <row r="49" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
@@ -60072,7 +60063,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="110" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="53">
@@ -60201,7 +60192,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="30">
         <v>45566</v>
       </c>
@@ -60622,7 +60613,7 @@
     </row>
     <row r="12" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="56">
@@ -60751,7 +60742,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="30">
         <f>B2</f>
         <v>45566</v>
@@ -61311,7 +61302,7 @@
     </row>
     <row r="27" spans="1:34" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="114" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="55">
@@ -61440,7 +61431,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="30">
         <f>B2</f>
         <v>45566</v>
@@ -61788,39 +61779,39 @@
       <c r="A36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="123" t="s">
+      <c r="B36" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="124"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
-      <c r="K36" s="124"/>
-      <c r="L36" s="124"/>
-      <c r="M36" s="124"/>
-      <c r="N36" s="124"/>
-      <c r="O36" s="124"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="124"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="124"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="124"/>
-      <c r="AB36" s="124"/>
-      <c r="AC36" s="124"/>
-      <c r="AD36" s="124"/>
-      <c r="AE36" s="124"/>
-      <c r="AF36" s="125"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="122"/>
+      <c r="I36" s="122"/>
+      <c r="J36" s="122"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="122"/>
+      <c r="M36" s="122"/>
+      <c r="N36" s="122"/>
+      <c r="O36" s="122"/>
+      <c r="P36" s="122"/>
+      <c r="Q36" s="122"/>
+      <c r="R36" s="122"/>
+      <c r="S36" s="122"/>
+      <c r="T36" s="122"/>
+      <c r="U36" s="122"/>
+      <c r="V36" s="122"/>
+      <c r="W36" s="122"/>
+      <c r="X36" s="122"/>
+      <c r="Y36" s="122"/>
+      <c r="Z36" s="122"/>
+      <c r="AA36" s="122"/>
+      <c r="AB36" s="122"/>
+      <c r="AC36" s="122"/>
+      <c r="AD36" s="122"/>
+      <c r="AE36" s="122"/>
+      <c r="AF36" s="123"/>
     </row>
     <row r="37" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
@@ -61894,7 +61885,7 @@
     </row>
     <row r="39" spans="1:32" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="116" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="54">
@@ -62023,7 +62014,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="30">
         <f>B2</f>
         <v>45566</v>
@@ -62369,39 +62360,39 @@
       <c r="A48" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="123" t="s">
+      <c r="B48" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="124"/>
-      <c r="K48" s="124"/>
-      <c r="L48" s="124"/>
-      <c r="M48" s="124"/>
-      <c r="N48" s="124"/>
-      <c r="O48" s="124"/>
-      <c r="P48" s="124"/>
-      <c r="Q48" s="124"/>
-      <c r="R48" s="124"/>
-      <c r="S48" s="124"/>
-      <c r="T48" s="124"/>
-      <c r="U48" s="124"/>
-      <c r="V48" s="124"/>
-      <c r="W48" s="124"/>
-      <c r="X48" s="124"/>
-      <c r="Y48" s="124"/>
-      <c r="Z48" s="124"/>
-      <c r="AA48" s="124"/>
-      <c r="AB48" s="124"/>
-      <c r="AC48" s="124"/>
-      <c r="AD48" s="124"/>
-      <c r="AE48" s="124"/>
-      <c r="AF48" s="125"/>
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="122"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="122"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="122"/>
+      <c r="S48" s="122"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="122"/>
+      <c r="V48" s="122"/>
+      <c r="W48" s="122"/>
+      <c r="X48" s="122"/>
+      <c r="Y48" s="122"/>
+      <c r="Z48" s="122"/>
+      <c r="AA48" s="122"/>
+      <c r="AB48" s="122"/>
+      <c r="AC48" s="122"/>
+      <c r="AD48" s="122"/>
+      <c r="AE48" s="122"/>
+      <c r="AF48" s="123"/>
     </row>
     <row r="49" spans="1:32" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">

--- a/data/Jabal Omar Hyatt Regency.xlsx
+++ b/data/Jabal Omar Hyatt Regency.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGR-TANTAWY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF46A74B-D464-45D8-AAB9-D9CD7BE00B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7E0129-83D5-4693-BD1F-6D7D4AA030DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="26" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46162,7 +46162,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
+      <c r="S3" s="23"/>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>

--- a/data/Jabal Omar Hyatt Regency.xlsx
+++ b/data/Jabal Omar Hyatt Regency.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGR-TANTAWY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7E0129-83D5-4693-BD1F-6D7D4AA030DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17232C81-8361-4D0B-BF9C-4D397EA806F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="26" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46171,7 +46171,7 @@
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
+      <c r="AB3" s="23"/>
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7"/>
